--- a/Day 5.xlsx
+++ b/Day 5.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70b5eb17ece67e4a/Desktop/itvedanth/Demart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B537CF5-B2ED-4690-BE96-D877F7349381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{8B537CF5-B2ED-4690-BE96-D877F7349381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22E0C877-8B36-44D0-898D-9B9015F7E77B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{0E3DAD9A-5736-4EBC-A780-CC4D82C18E05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Reg No</t>
   </si>
@@ -101,7 +102,19 @@
     <t>HR</t>
   </si>
   <si>
-    <t>Rank</t>
+    <t xml:space="preserve">Age </t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>OR</t>
   </si>
 </sst>
 </file>
@@ -183,7 +196,70 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="8" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="8" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="8" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="8" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="8" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="9" tint="0.39994506668294322"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -205,56 +281,28 @@
       <font>
         <b/>
         <i/>
+        <color theme="9" tint="0.39994506668294322"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
         <color theme="8" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="8" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="8" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="8" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="8" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -268,22 +316,25 @@
       <font>
         <b/>
         <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
         <color theme="3" tint="0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="8" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="3" tint="0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -296,11 +347,35 @@
       <font>
         <b/>
         <i/>
+        <color theme="3" tint="0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
         <color theme="8" tint="-0.24994659260841701"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <color theme="3" tint="0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i/>
         <color theme="5" tint="-0.24994659260841701"/>
@@ -310,28 +385,7 @@
       <font>
         <b/>
         <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
+        <color theme="8" tint="-0.24994659260841701"/>
       </font>
     </dxf>
     <dxf>
@@ -340,160 +394,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="3" tint="0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -513,10 +413,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -846,7 +742,7 @@
     <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -861,6 +757,9 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -891,7 +790,13 @@
         <v>15</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -922,11 +827,20 @@
         <v>85.333333333333329</v>
       </c>
       <c r="I3" t="str">
-        <f>IF(H3&gt;80,"Best","Low")</f>
+        <f>IF(H3&gt;70,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="J3" t="str">
+        <f>IF(H3&gt;80,"O",IF(H3&gt;70,"A",IF(H3&lt;70,"Re")))</f>
+        <v>O</v>
+      </c>
+      <c r="K3" t="str">
+        <f>IF(AND(C3="AI&amp;DS",I3="Pass"),"Best","Average")</f>
         <v>Best</v>
       </c>
-      <c r="J3">
-        <v>1</v>
+      <c r="L3" t="str">
+        <f>IF(OR(C3="AI&amp;DS",I3="Pass"),"Best","Average")</f>
+        <v>Best</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -957,11 +871,20 @@
         <v>68.333333333333329</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4:I8" si="2">IF(H4&gt;80,"Best","Low")</f>
-        <v>Low</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
+        <f t="shared" ref="I4:I8" si="2">IF(H4&gt;70,"Pass","Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" ref="J4:J8" si="3">IF(H4&gt;80,"O",IF(H4&gt;70,"A",IF(H4&lt;70,"Re")))</f>
+        <v>Re</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" ref="K4:K8" si="4">IF(AND(C4="AI&amp;DS",I4="Pass"),"Best","Average")</f>
+        <v>Average</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" ref="L4:L8" si="5">IF(OR(C4="AI&amp;DS",I4="Pass"),"Best","Average")</f>
+        <v>Best</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -981,22 +904,31 @@
         <v>78</v>
       </c>
       <c r="F5">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>83.666666666666671</v>
+        <v>82.666666666666671</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="2"/>
+        <v>Pass</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="3"/>
+        <v>O</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="4"/>
         <v>Best</v>
       </c>
-      <c r="J5">
-        <v>3</v>
+      <c r="L5" t="str">
+        <f t="shared" si="5"/>
+        <v>Best</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -1028,10 +960,19 @@
       </c>
       <c r="I6" t="str">
         <f t="shared" si="2"/>
+        <v>Pass</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="3"/>
+        <v>O</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="4"/>
+        <v>Average</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="5"/>
         <v>Best</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -1063,10 +1004,19 @@
       </c>
       <c r="I7" t="str">
         <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
+        <v>Fail</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="3"/>
+        <v>Re</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="4"/>
+        <v>Average</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="5"/>
+        <v>Average</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -1080,28 +1030,37 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="E8">
         <v>79</v>
       </c>
       <c r="F8">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>61.666666666666664</v>
+        <v>77</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="J8">
-        <v>6</v>
+        <v>Pass</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="4"/>
+        <v>Average</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="5"/>
+        <v>Best</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -1115,15 +1074,15 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D10">
         <f>AVERAGE(D3:D8)</f>
-        <v>77</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="E10">
-        <f t="shared" ref="E10:F10" si="3">AVERAGE(E3:E8)</f>
+        <f t="shared" ref="E10:F10" si="6">AVERAGE(E3:E8)</f>
         <v>78.166666666666671</v>
       </c>
       <c r="F10">
-        <f t="shared" si="3"/>
-        <v>70.833333333333329</v>
+        <f t="shared" si="6"/>
+        <v>74.333333333333329</v>
       </c>
       <c r="P10">
         <v>3</v>
@@ -1213,38 +1172,68 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D2:F8">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="lessThan">
-      <formula>50</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="between">
       <formula>50</formula>
       <formula>70</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I8">
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="Best">
-      <formula>NOT(ISERROR(SEARCH("Best",I3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",I3)))</formula>
+    <cfRule type="cellIs" dxfId="19" priority="22" operator="lessThan">
+      <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H8">
-    <cfRule type="aboveAverage" dxfId="4" priority="10"/>
-    <cfRule type="iconSet" priority="4">
+    <cfRule type="iconSet" priority="10">
       <iconSet>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
         <cfvo type="percent" val="67"/>
       </iconSet>
     </cfRule>
+    <cfRule type="aboveAverage" dxfId="1" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I8">
+    <cfRule type="containsText" dxfId="5" priority="15" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",I3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="Best">
+      <formula>NOT(ISERROR(SEARCH("Best",I3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="P">
+      <formula>NOT(ISERROR(SEARCH("P",I3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",I3)))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J8">
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{92847742-B041-42FD-8F39-D0E8F9887E14}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="8" tint="-0.249977111117893"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5057E199-A38A-4749-81CC-D10488A193B4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1256,40 +1245,16 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="8" tint="-0.249977111117893"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5057E199-A38A-4749-81CC-D10488A193B4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92847742-B041-42FD-8F39-D0E8F9887E14}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P23">
-    <cfRule type="expression" priority="3">
+    <cfRule type="expression" dxfId="18" priority="7">
+      <formula>ISODD($P8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="8">
       <formula>ISEVEN($P8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" priority="9">
       <formula>ISEVEN($P8)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>ISODD($P8)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1298,7 +1263,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{F7EAFA4D-645D-4342-A5C3-58DA569F0DEA}">
+          <x14:cfRule type="iconSet" priority="11" id="{F7EAFA4D-645D-4342-A5C3-58DA569F0DEA}">
             <x14:iconSet iconSet="4Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -1313,6 +1278,90 @@
                 <xm:f>80</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <x14:cfRule type="iconSet" priority="4" id="{8B4398E0-8491-4403-A6B6-1F1EA76D59E2}">
+            <x14:iconSet iconSet="5Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>20</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>50</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>70</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>80</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <x14:cfRule type="iconSet" priority="3" id="{6516FA79-4D8B-4888-8A2E-54997A75637F}">
+            <x14:iconSet iconSet="4Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>25</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>50</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>75</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <x14:cfRule type="iconSet" priority="2" id="{F0D6E87E-5CFC-4261-92D7-491E3B6901CF}">
+            <x14:iconSet iconSet="5Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>20</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>50</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>65</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>80</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <x14:cfRule type="iconSet" priority="1" id="{F670CBBF-B9F0-4E1A-9BAC-81C40633D94B}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>50</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>75</xm:f>
+              </x14:cfvo>
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
               <x14:cfIcon iconSet="3Arrows" iconId="1"/>
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
@@ -1321,13 +1370,11 @@
           <xm:sqref>H3:H8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79D5BAB2-7E8B-4051-BA6F-885A0152C75F}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+          <x14:cfRule type="dataBar" id="{92847742-B041-42FD-8F39-D0E8F9887E14}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
@@ -1339,11 +1386,13 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{92847742-B041-42FD-8F39-D0E8F9887E14}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+          <x14:cfRule type="dataBar" id="{79D5BAB2-7E8B-4051-BA6F-885A0152C75F}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
@@ -1353,4 +1402,38 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0F38CDB-70BC-40AF-81DC-D506258561CC}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1">
+        <v>15</v>
+      </c>
+      <c r="C1" t="str">
+        <f>IF(B1&gt;18,"Eligible","Not Eligible")</f>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4" t="str">
+        <f>IF(B4&gt;80,"O",IF(B4&gt;70,"A","F"))</f>
+        <v>F</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>